--- a/media/Levels/Level_9.xlsx
+++ b/media/Levels/Level_9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E55F9938-B179-411F-B440-95AB2E03A3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263B069E-9ABE-40AA-BBBC-850386BF21BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="BX74" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BY74" s="2">
         <v>0</v>

--- a/media/Levels/Level_9.xlsx
+++ b/media/Levels/Level_9.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263B069E-9ABE-40AA-BBBC-850386BF21BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B1E2AD1-A018-4C50-8E6F-08ABF81DEE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_9" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5181,21 +5181,6 @@
       <c r="BH47" s="1">
         <v>0</v>
       </c>
-      <c r="BR47" s="3">
-        <v>0</v>
-      </c>
-      <c r="BS47" s="3">
-        <v>0</v>
-      </c>
-      <c r="BT47" s="3">
-        <v>0</v>
-      </c>
-      <c r="BU47" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV47" s="3">
-        <v>0</v>
-      </c>
       <c r="CP47" s="1">
         <v>5</v>
       </c>
@@ -5411,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="BT49" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU49" s="3">
         <v>0</v>
@@ -5521,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="BT50" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU50" s="3">
         <v>0</v>
@@ -5716,11 +5701,26 @@
       <c r="BE52" s="1">
         <v>0</v>
       </c>
+      <c r="BR52" s="3">
+        <v>0</v>
+      </c>
+      <c r="BS52" s="3">
+        <v>0</v>
+      </c>
+      <c r="BT52" s="3">
+        <v>0</v>
+      </c>
+      <c r="BU52" s="3">
+        <v>0</v>
+      </c>
+      <c r="BV52" s="3">
+        <v>0</v>
+      </c>
       <c r="CN52" s="1">
         <v>0</v>
       </c>
       <c r="CS52" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DC52" s="4">
         <v>9</v>
@@ -5799,6 +5799,9 @@
       <c r="BE53" s="1">
         <v>0</v>
       </c>
+      <c r="BU53" s="1">
+        <v>0</v>
+      </c>
       <c r="CM53" s="1">
         <v>5</v>
       </c>
@@ -5882,6 +5885,9 @@
       <c r="BE54" s="1">
         <v>4</v>
       </c>
+      <c r="BV54" s="1">
+        <v>6</v>
+      </c>
       <c r="CL54" s="1">
         <v>0</v>
       </c>
@@ -5965,11 +5971,14 @@
       <c r="BE55" s="1">
         <v>0</v>
       </c>
+      <c r="BW55" s="1">
+        <v>0</v>
+      </c>
       <c r="CK55" s="1">
         <v>0</v>
       </c>
       <c r="CV55" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ55" s="4">
         <v>9</v>
@@ -6048,6 +6057,9 @@
       <c r="BE56" s="1">
         <v>0</v>
       </c>
+      <c r="BX56" s="1">
+        <v>0</v>
+      </c>
       <c r="CJ56" s="1">
         <v>5</v>
       </c>
@@ -6131,6 +6143,36 @@
       <c r="BE57" s="1">
         <v>4</v>
       </c>
+      <c r="BY57" s="1">
+        <v>6</v>
+      </c>
+      <c r="BZ57" s="5">
+        <v>0</v>
+      </c>
+      <c r="CA57" s="4">
+        <v>7</v>
+      </c>
+      <c r="CB57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD57" s="4">
+        <v>7</v>
+      </c>
+      <c r="CE57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF57" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG57" s="4">
+        <v>7</v>
+      </c>
+      <c r="CH57" s="4">
+        <v>0</v>
+      </c>
       <c r="CI57" s="1">
         <v>0</v>
       </c>
@@ -6214,32 +6256,8 @@
       <c r="BZ58" s="1">
         <v>0</v>
       </c>
-      <c r="CA58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CB58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD58" s="4">
-        <v>7</v>
-      </c>
-      <c r="CE58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF58" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG58" s="4">
-        <v>7</v>
-      </c>
-      <c r="CH58" s="4">
-        <v>0</v>
-      </c>
       <c r="CY58" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="EB58" s="3">
         <v>0</v>
@@ -6270,7 +6288,7 @@
       <c r="BE59" s="1">
         <v>0</v>
       </c>
-      <c r="BZ59" s="1">
+      <c r="CA59" s="1">
         <v>0</v>
       </c>
       <c r="CZ59" s="1">
@@ -6305,8 +6323,8 @@
       <c r="BE60" s="1">
         <v>4</v>
       </c>
-      <c r="CA60" s="1">
-        <v>5</v>
+      <c r="CB60" s="1">
+        <v>6</v>
       </c>
       <c r="DA60" s="1">
         <v>0</v>
@@ -6340,7 +6358,7 @@
       <c r="BE61" s="1">
         <v>0</v>
       </c>
-      <c r="CB61" s="1">
+      <c r="CC61" s="1">
         <v>0</v>
       </c>
       <c r="DB61" s="1">
@@ -6417,7 +6435,7 @@
       <c r="BE62" s="1">
         <v>0</v>
       </c>
-      <c r="CC62" s="1">
+      <c r="CD62" s="1">
         <v>0</v>
       </c>
       <c r="DC62" s="1">
@@ -6452,8 +6470,8 @@
       <c r="BE63" s="1">
         <v>4</v>
       </c>
-      <c r="CD63" s="1">
-        <v>5</v>
+      <c r="CE63" s="1">
+        <v>6</v>
       </c>
       <c r="DD63" s="1">
         <v>0</v>
@@ -6472,7 +6490,7 @@
       <c r="BE64" s="1">
         <v>0</v>
       </c>
-      <c r="CE64" s="1">
+      <c r="CF64" s="1">
         <v>0</v>
       </c>
       <c r="DE64" s="1">
@@ -6629,6 +6647,9 @@
       <c r="CG66" s="2">
         <v>0</v>
       </c>
+      <c r="CH66" s="1">
+        <v>6</v>
+      </c>
       <c r="DG66" s="1">
         <v>0</v>
       </c>
@@ -6706,6 +6727,9 @@
       <c r="CG67" s="2">
         <v>0</v>
       </c>
+      <c r="CI67" s="1">
+        <v>0</v>
+      </c>
       <c r="DH67" s="1">
         <v>6</v>
       </c>
@@ -6783,6 +6807,9 @@
       <c r="CG68" s="2">
         <v>0</v>
       </c>
+      <c r="CJ68" s="1">
+        <v>0</v>
+      </c>
       <c r="DI68" s="1">
         <v>0</v>
       </c>
@@ -6860,6 +6887,9 @@
       <c r="CG69" s="2">
         <v>0</v>
       </c>
+      <c r="CK69" s="1">
+        <v>6</v>
+      </c>
       <c r="DJ69" s="1">
         <v>0</v>
       </c>
@@ -6935,6 +6965,9 @@
         <v>0</v>
       </c>
       <c r="CG70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL70" s="1">
         <v>0</v>
       </c>
       <c r="DK70" s="1">
@@ -9838,21 +9871,27 @@
         <v>0</v>
       </c>
       <c r="BT101" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU101" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV101" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW101" s="1">
         <v>3</v>
       </c>
-      <c r="BV101" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW101" s="1">
-        <v>0</v>
-      </c>
       <c r="BX101" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY101" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ101" s="1">
         <v>3</v>
       </c>
-      <c r="BY101" s="1">
+      <c r="CA101" s="1">
         <v>0</v>
       </c>
       <c r="CG101" s="1">
@@ -10640,7 +10679,7 @@
         <v>4</v>
       </c>
       <c r="BB109" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BT109" s="4">
         <v>10</v>

--- a/media/Levels/Level_9.xlsx
+++ b/media/Levels/Level_9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B1E2AD1-A018-4C50-8E6F-08ABF81DEE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{960963E5-49DC-46DB-9251-47485982F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -9835,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="BH101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI101" s="1">
         <v>0</v>
@@ -9844,7 +9844,7 @@
         <v>0</v>
       </c>
       <c r="BK101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL101" s="1">
         <v>0</v>
@@ -9853,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="BN101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BO101" s="1">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="BQ101" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BR101" s="1">
         <v>0</v>
@@ -9871,7 +9871,7 @@
         <v>0</v>
       </c>
       <c r="BT101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU101" s="1">
         <v>0</v>
@@ -9880,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="BW101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BX101" s="1">
         <v>0</v>
@@ -9889,7 +9889,7 @@
         <v>0</v>
       </c>
       <c r="BZ101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CA101" s="1">
         <v>0</v>
@@ -9901,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="CI101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ101" s="1">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>0</v>
       </c>
       <c r="CL101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CM101" s="1">
         <v>0</v>
@@ -9919,16 +9919,16 @@
         <v>0</v>
       </c>
       <c r="CO101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CP101" s="1">
         <v>0</v>
       </c>
       <c r="CQ101" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CR101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CS101" s="1">
         <v>0</v>
@@ -9937,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="CU101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV101" s="1">
         <v>0</v>
@@ -9946,12 +9946,15 @@
         <v>0</v>
       </c>
       <c r="CX101" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CY101" s="1">
         <v>0</v>
       </c>
       <c r="CZ101" s="1">
+        <v>0</v>
+      </c>
+      <c r="DA101" s="1">
         <v>0</v>
       </c>
       <c r="EI101" s="3">
@@ -10044,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="CG102" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CK102" s="1">
         <v>0</v>
@@ -10142,7 +10145,7 @@
         <v>6</v>
       </c>
       <c r="CG103" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CK103" s="1">
         <v>4</v>
@@ -10338,7 +10341,7 @@
         <v>0</v>
       </c>
       <c r="CG105" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CK105" s="4">
         <v>0</v>
@@ -10421,7 +10424,7 @@
         <v>6</v>
       </c>
       <c r="CG106" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CK106" s="4">
         <v>8</v>
@@ -10596,7 +10599,7 @@
         <v>0</v>
       </c>
       <c r="CG108" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CK108" s="4">
         <v>0</v>
@@ -10685,7 +10688,7 @@
         <v>10</v>
       </c>
       <c r="CG109" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CK109" s="4">
         <v>8</v>

--- a/media/Levels/Level_9.xlsx
+++ b/media/Levels/Level_9.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{960963E5-49DC-46DB-9251-47485982F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F39DF2-ACA0-4BF9-A5AA-91C8DEB284EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -8558,7 +8558,7 @@
       <c r="AR87" s="1">
         <v>0</v>
       </c>
-      <c r="BO87" s="1">
+      <c r="BO87" s="5">
         <v>0</v>
       </c>
       <c r="DH87" s="1">
@@ -8596,8 +8596,8 @@
       <c r="AR88" s="1">
         <v>4</v>
       </c>
-      <c r="BN88" s="1">
-        <v>5</v>
+      <c r="BN88" s="5">
+        <v>9</v>
       </c>
       <c r="CR88" s="3">
         <v>0</v>
@@ -8649,7 +8649,7 @@
       <c r="AR89" s="1">
         <v>0</v>
       </c>
-      <c r="BM89" s="1">
+      <c r="BM89" s="5">
         <v>0</v>
       </c>
       <c r="CR89" s="3">

--- a/media/Levels/Level_9.xlsx
+++ b/media/Levels/Level_9.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F39DF2-ACA0-4BF9-A5AA-91C8DEB284EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ED3AF2A-1333-4850-9821-9F927C78A136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -952,6 +952,15 @@
       <c r="BX7" s="1">
         <v>0</v>
       </c>
+      <c r="CL7" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM7" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN7" s="2">
+        <v>0</v>
+      </c>
       <c r="CO7" s="2">
         <v>0</v>
       </c>
@@ -1001,15 +1010,6 @@
         <v>0</v>
       </c>
       <c r="DE7" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF7" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG7" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH7" s="2">
         <v>0</v>
       </c>
       <c r="ET7" s="1">
@@ -1023,6 +1023,15 @@
       <c r="BX8" s="1">
         <v>0</v>
       </c>
+      <c r="CL8" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM8" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN8" s="2">
+        <v>0</v>
+      </c>
       <c r="CO8" s="2">
         <v>0</v>
       </c>
@@ -1072,15 +1081,6 @@
         <v>0</v>
       </c>
       <c r="DE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG8" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH8" s="2">
         <v>0</v>
       </c>
       <c r="ET8" s="1">
@@ -1094,6 +1094,15 @@
       <c r="BX9" s="1">
         <v>4</v>
       </c>
+      <c r="CL9" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM9" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN9" s="2">
+        <v>0</v>
+      </c>
       <c r="CO9" s="2">
         <v>0</v>
       </c>
@@ -1143,15 +1152,6 @@
         <v>0</v>
       </c>
       <c r="DE9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG9" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH9" s="2">
         <v>0</v>
       </c>
       <c r="ET9" s="1">
@@ -1180,6 +1180,15 @@
       <c r="BX10" s="1">
         <v>0</v>
       </c>
+      <c r="CL10" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM10" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN10" s="2">
+        <v>0</v>
+      </c>
       <c r="CO10" s="2">
         <v>0</v>
       </c>
@@ -1229,15 +1238,6 @@
         <v>0</v>
       </c>
       <c r="DE10" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF10" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG10" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH10" s="2">
         <v>0</v>
       </c>
       <c r="ET10" s="1">
@@ -1266,6 +1266,15 @@
       <c r="BX11" s="1">
         <v>0</v>
       </c>
+      <c r="CL11" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM11" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN11" s="2">
+        <v>0</v>
+      </c>
       <c r="CO11" s="2">
         <v>0</v>
       </c>
@@ -1315,15 +1324,6 @@
         <v>0</v>
       </c>
       <c r="DE11" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF11" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG11" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH11" s="2">
         <v>0</v>
       </c>
       <c r="ET11" s="1">
@@ -1412,6 +1412,15 @@
       <c r="BX12" s="1">
         <v>4</v>
       </c>
+      <c r="CL12" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM12" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN12" s="2">
+        <v>0</v>
+      </c>
       <c r="CO12" s="2">
         <v>0</v>
       </c>
@@ -1461,15 +1470,6 @@
         <v>0</v>
       </c>
       <c r="DE12" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF12" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG12" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH12" s="2">
         <v>0</v>
       </c>
       <c r="ET12" s="1">
@@ -1558,6 +1558,15 @@
       <c r="BX13" s="1">
         <v>0</v>
       </c>
+      <c r="CL13" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM13" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN13" s="2">
+        <v>0</v>
+      </c>
       <c r="CO13" s="2">
         <v>0</v>
       </c>
@@ -1607,15 +1616,6 @@
         <v>0</v>
       </c>
       <c r="DE13" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF13" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG13" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH13" s="2">
         <v>0</v>
       </c>
       <c r="ET13" s="1">
@@ -1704,6 +1704,15 @@
       <c r="BX14" s="1">
         <v>0</v>
       </c>
+      <c r="CL14" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM14" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN14" s="2">
+        <v>0</v>
+      </c>
       <c r="CO14" s="2">
         <v>0</v>
       </c>
@@ -1753,15 +1762,6 @@
         <v>0</v>
       </c>
       <c r="DE14" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF14" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG14" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH14" s="2">
         <v>0</v>
       </c>
       <c r="EB14" s="3">
@@ -1850,6 +1850,15 @@
       <c r="BX15" s="1">
         <v>4</v>
       </c>
+      <c r="CL15" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM15" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN15" s="2">
+        <v>0</v>
+      </c>
       <c r="CO15" s="2">
         <v>0</v>
       </c>
@@ -1899,15 +1908,6 @@
         <v>0</v>
       </c>
       <c r="DE15" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF15" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG15" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH15" s="2">
         <v>0</v>
       </c>
       <c r="EB15" s="3">
@@ -1996,6 +1996,15 @@
       <c r="BX16" s="1">
         <v>0</v>
       </c>
+      <c r="CL16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN16" s="2">
+        <v>0</v>
+      </c>
       <c r="CO16" s="2">
         <v>0</v>
       </c>
@@ -2018,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="CV16" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CW16" s="2">
         <v>0</v>
@@ -2027,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="CY16" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CZ16" s="2">
         <v>0</v>
@@ -2045,15 +2054,6 @@
         <v>0</v>
       </c>
       <c r="DE16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH16" s="2">
         <v>0</v>
       </c>
       <c r="EB16" s="3">
@@ -2142,6 +2142,15 @@
       <c r="BX17" s="1">
         <v>0</v>
       </c>
+      <c r="CL17" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM17" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN17" s="2">
+        <v>0</v>
+      </c>
       <c r="CO17" s="2">
         <v>0</v>
       </c>
@@ -2191,15 +2200,6 @@
         <v>0</v>
       </c>
       <c r="DE17" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF17" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG17" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH17" s="2">
         <v>0</v>
       </c>
       <c r="EB17" s="3">
@@ -2288,6 +2288,15 @@
       <c r="BX18" s="1">
         <v>4</v>
       </c>
+      <c r="CL18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN18" s="2">
+        <v>0</v>
+      </c>
       <c r="CO18" s="2">
         <v>0</v>
       </c>
@@ -2337,15 +2346,6 @@
         <v>0</v>
       </c>
       <c r="DE18" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF18" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG18" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH18" s="2">
         <v>0</v>
       </c>
       <c r="EB18" s="3">
@@ -2449,6 +2449,15 @@
       <c r="BX19" s="1">
         <v>0</v>
       </c>
+      <c r="CL19" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM19" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN19" s="2">
+        <v>0</v>
+      </c>
       <c r="CO19" s="2">
         <v>0</v>
       </c>
@@ -2498,15 +2507,6 @@
         <v>0</v>
       </c>
       <c r="DE19" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF19" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG19" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH19" s="2">
         <v>0</v>
       </c>
       <c r="ET19" s="1">
@@ -2595,6 +2595,15 @@
       <c r="BX20" s="1">
         <v>0</v>
       </c>
+      <c r="CL20" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM20" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN20" s="2">
+        <v>0</v>
+      </c>
       <c r="CO20" s="2">
         <v>0</v>
       </c>
@@ -2644,15 +2653,6 @@
         <v>0</v>
       </c>
       <c r="DE20" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF20" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG20" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH20" s="2">
         <v>0</v>
       </c>
       <c r="ET20" s="1">
@@ -2774,6 +2774,9 @@
       <c r="BX21" s="1">
         <v>4</v>
       </c>
+      <c r="CD21" s="3">
+        <v>0</v>
+      </c>
       <c r="CE21" s="3">
         <v>0</v>
       </c>
@@ -2786,7 +2789,13 @@
       <c r="CH21" s="3">
         <v>0</v>
       </c>
-      <c r="CI21" s="3">
+      <c r="CL21" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM21" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN21" s="2">
         <v>0</v>
       </c>
       <c r="CO21" s="2">
@@ -2838,15 +2847,6 @@
         <v>0</v>
       </c>
       <c r="DE21" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF21" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG21" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH21" s="2">
         <v>0</v>
       </c>
       <c r="ET21" s="1">
@@ -2950,6 +2950,9 @@
       <c r="BX22" s="1">
         <v>0</v>
       </c>
+      <c r="CD22" s="3">
+        <v>0</v>
+      </c>
       <c r="CE22" s="3">
         <v>0</v>
       </c>
@@ -2962,7 +2965,13 @@
       <c r="CH22" s="3">
         <v>0</v>
       </c>
-      <c r="CI22" s="3">
+      <c r="CL22" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM22" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN22" s="2">
         <v>0</v>
       </c>
       <c r="CO22" s="2">
@@ -3014,15 +3023,6 @@
         <v>0</v>
       </c>
       <c r="DE22" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF22" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG22" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH22" s="2">
         <v>0</v>
       </c>
       <c r="ET22" s="1">
@@ -3126,19 +3126,28 @@
       <c r="BX23" s="1">
         <v>0</v>
       </c>
+      <c r="CD23" s="3">
+        <v>0</v>
+      </c>
       <c r="CE23" s="3">
         <v>0</v>
       </c>
       <c r="CF23" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CG23" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CH23" s="3">
         <v>0</v>
       </c>
-      <c r="CI23" s="3">
+      <c r="CL23" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM23" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN23" s="2">
         <v>0</v>
       </c>
       <c r="CO23" s="2">
@@ -3190,15 +3199,6 @@
         <v>0</v>
       </c>
       <c r="DE23" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF23" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG23" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH23" s="2">
         <v>0</v>
       </c>
       <c r="ET23" s="1">
@@ -3290,6 +3290,9 @@
       <c r="BX24" s="1">
         <v>4</v>
       </c>
+      <c r="CD24" s="3">
+        <v>0</v>
+      </c>
       <c r="CE24" s="3">
         <v>0</v>
       </c>
@@ -3302,7 +3305,13 @@
       <c r="CH24" s="3">
         <v>0</v>
       </c>
-      <c r="CI24" s="3">
+      <c r="CL24" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM24" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN24" s="2">
         <v>0</v>
       </c>
       <c r="CO24" s="2">
@@ -3354,15 +3363,6 @@
         <v>0</v>
       </c>
       <c r="DE24" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF24" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG24" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH24" s="2">
         <v>0</v>
       </c>
       <c r="ET24" s="1">
@@ -3454,6 +3454,9 @@
       <c r="BX25" s="1">
         <v>0</v>
       </c>
+      <c r="CD25" s="3">
+        <v>0</v>
+      </c>
       <c r="CE25" s="3">
         <v>0</v>
       </c>
@@ -3466,7 +3469,13 @@
       <c r="CH25" s="3">
         <v>0</v>
       </c>
-      <c r="CI25" s="3">
+      <c r="CL25" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM25" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN25" s="2">
         <v>0</v>
       </c>
       <c r="CO25" s="2">
@@ -3478,8 +3487,8 @@
       <c r="CQ25" s="2">
         <v>0</v>
       </c>
-      <c r="CR25" s="2">
-        <v>0</v>
+      <c r="CR25" s="1">
+        <v>4</v>
       </c>
       <c r="CS25" s="2">
         <v>0</v>
@@ -3518,15 +3527,6 @@
         <v>0</v>
       </c>
       <c r="DE25" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF25" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG25" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH25" s="2">
         <v>0</v>
       </c>
       <c r="ET25" s="1">
@@ -3609,6 +3609,15 @@
       <c r="BX26" s="1">
         <v>0</v>
       </c>
+      <c r="CL26" s="2">
+        <v>0</v>
+      </c>
+      <c r="CM26" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN26" s="2">
+        <v>0</v>
+      </c>
       <c r="CO26" s="2">
         <v>0</v>
       </c>
@@ -3618,7 +3627,7 @@
       <c r="CQ26" s="2">
         <v>0</v>
       </c>
-      <c r="CR26" s="2">
+      <c r="CR26" s="1">
         <v>0</v>
       </c>
       <c r="CS26" s="2">
@@ -3658,15 +3667,6 @@
         <v>0</v>
       </c>
       <c r="DE26" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF26" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG26" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH26" s="2">
         <v>0</v>
       </c>
       <c r="ET26" s="1">
@@ -3894,8 +3894,8 @@
       <c r="AJ29" s="2">
         <v>0</v>
       </c>
-      <c r="AK29" s="2">
-        <v>0</v>
+      <c r="AK29" s="1">
+        <v>4</v>
       </c>
       <c r="AL29" s="2">
         <v>0</v>
@@ -3992,7 +3992,7 @@
       <c r="AJ30" s="2">
         <v>0</v>
       </c>
-      <c r="AK30" s="2">
+      <c r="AK30" s="1">
         <v>0</v>
       </c>
       <c r="AL30" s="2">
@@ -4090,7 +4090,7 @@
       <c r="AJ31" s="2">
         <v>0</v>
       </c>
-      <c r="AK31" s="2">
+      <c r="AK31" s="1">
         <v>0</v>
       </c>
       <c r="AL31" s="2">
@@ -8464,8 +8464,8 @@
       <c r="BQ85" s="1">
         <v>5</v>
       </c>
-      <c r="DF85" s="1">
-        <v>0</v>
+      <c r="DH85" s="1">
+        <v>6</v>
       </c>
       <c r="DW85" s="4">
         <v>0</v>
@@ -8520,8 +8520,8 @@
       <c r="BP86" s="1">
         <v>0</v>
       </c>
-      <c r="DG86" s="1">
-        <v>6</v>
+      <c r="DI86" s="1">
+        <v>0</v>
       </c>
       <c r="DV86" s="4">
         <v>0</v>
@@ -8561,7 +8561,7 @@
       <c r="BO87" s="5">
         <v>0</v>
       </c>
-      <c r="DH87" s="1">
+      <c r="DJ87" s="1">
         <v>0</v>
       </c>
       <c r="DU87" s="4">
@@ -8614,8 +8614,8 @@
       <c r="CV88" s="3">
         <v>0</v>
       </c>
-      <c r="DI88" s="1">
-        <v>0</v>
+      <c r="DK88" s="1">
+        <v>6</v>
       </c>
       <c r="DT88" s="4">
         <v>0</v>
@@ -8667,8 +8667,8 @@
       <c r="CV89" s="3">
         <v>0</v>
       </c>
-      <c r="DJ89" s="1">
-        <v>6</v>
+      <c r="DL89" s="1">
+        <v>0</v>
       </c>
       <c r="DS89" s="4">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       <c r="CV90" s="3">
         <v>0</v>
       </c>
-      <c r="DK90" s="1">
+      <c r="DM90" s="1">
         <v>0</v>
       </c>
       <c r="DR90" s="4">
@@ -8902,8 +8902,8 @@
       <c r="CV91" s="3">
         <v>0</v>
       </c>
-      <c r="DL91" s="1">
-        <v>0</v>
+      <c r="DN91" s="1">
+        <v>6</v>
       </c>
       <c r="DQ91" s="3">
         <v>0</v>
@@ -9024,8 +9024,8 @@
       <c r="CV92" s="3">
         <v>0</v>
       </c>
-      <c r="DM92" s="1">
-        <v>6</v>
+      <c r="DO92" s="1">
+        <v>0</v>
       </c>
       <c r="DQ92" s="3">
         <v>0</v>
@@ -9131,7 +9131,7 @@
       <c r="BK93" s="1">
         <v>6</v>
       </c>
-      <c r="DN93" s="1">
+      <c r="DP93" s="1">
         <v>0</v>
       </c>
       <c r="DQ93" s="3">
@@ -9238,11 +9238,8 @@
       <c r="BL94" s="1">
         <v>0</v>
       </c>
-      <c r="DO94" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ94" s="3">
-        <v>0</v>
+      <c r="DQ94" s="1">
+        <v>6</v>
       </c>
       <c r="DR94" s="3">
         <v>0</v>
@@ -9330,9 +9327,6 @@
       <c r="BM95" s="1">
         <v>0</v>
       </c>
-      <c r="DP95" s="1">
-        <v>6</v>
-      </c>
       <c r="DQ95" s="3">
         <v>0</v>
       </c>
@@ -9413,43 +9407,37 @@
       <c r="AJ96" s="2">
         <v>0</v>
       </c>
-      <c r="AK96" s="2">
+      <c r="AK96" s="1">
         <v>0</v>
       </c>
       <c r="AL96" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM96" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="1">
         <v>3</v>
       </c>
-      <c r="AN96" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO96" s="1">
-        <v>0</v>
-      </c>
       <c r="AP96" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR96" s="1">
         <v>3</v>
       </c>
-      <c r="AQ96" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR96" s="1">
-        <v>0</v>
-      </c>
       <c r="AS96" s="1">
-        <v>3</v>
-      </c>
-      <c r="AT96" s="1">
         <v>0</v>
       </c>
       <c r="BN96" s="1">
         <v>6</v>
       </c>
       <c r="DE96" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ96" s="1">
         <v>0</v>
       </c>
       <c r="ET96" s="1">

--- a/media/Levels/Level_9.xlsx
+++ b/media/Levels/Level_9.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ED3AF2A-1333-4850-9821-9F927C78A136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCCE12B5-7DCC-47B3-9C49-BD8A20A64255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -677,10 +677,10 @@
         <v>0</v>
       </c>
       <c r="BW1" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY1" s="1">
         <v>0</v>
@@ -14562,10 +14562,10 @@
         <v>0</v>
       </c>
       <c r="BW150" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY150" s="1">
         <v>0</v>
